--- a/artfynd/A 50838-2023 artfynd.xlsx
+++ b/artfynd/A 50838-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50838-2023 artfynd.xlsx
+++ b/artfynd/A 50838-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96881560</v>
+        <v>96881565</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547964.8613611215</v>
+        <v>547965</v>
       </c>
       <c r="R2" t="n">
-        <v>7049496.743075455</v>
+        <v>7049497</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +746,9 @@
           <t>2021-10-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +779,7 @@
         <v>96881562</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547964.8613611215</v>
+        <v>547965</v>
       </c>
       <c r="R3" t="n">
-        <v>7049496.743075455</v>
+        <v>7049497</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,19 +847,9 @@
           <t>2021-10-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96881566</v>
+        <v>96881560</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547962.0458654606</v>
+        <v>547965</v>
       </c>
       <c r="R4" t="n">
-        <v>7049535.466546086</v>
+        <v>7049497</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,19 +949,9 @@
           <t>2021-10-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96881565</v>
+        <v>96881566</v>
       </c>
       <c r="B5" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,26 +990,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547964.8613611215</v>
+        <v>547962</v>
       </c>
       <c r="R5" t="n">
-        <v>7049496.743075455</v>
+        <v>7049535</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,19 +1051,9 @@
           <t>2021-10-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 50838-2023 artfynd.xlsx
+++ b/artfynd/A 50838-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96881565</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96881562</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96881560</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,8 +1098,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96881566</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>